--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478832</v>
+        <v>122478614</v>
       </c>
       <c r="B2" t="n">
         <v>57749</v>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591009</v>
+        <v>591079</v>
       </c>
       <c r="R2" t="n">
-        <v>6440585</v>
+        <v>6440534</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478633</v>
+        <v>122478832</v>
       </c>
       <c r="B3" t="n">
-        <v>105308</v>
+        <v>57749</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +805,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591057</v>
+        <v>591009</v>
       </c>
       <c r="R3" t="n">
-        <v>6440531</v>
+        <v>6440585</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478814</v>
+        <v>122478809</v>
       </c>
       <c r="B4" t="n">
         <v>98202</v>
@@ -948,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591015</v>
+        <v>591050</v>
       </c>
       <c r="R4" t="n">
-        <v>6440575</v>
+        <v>6440530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478630</v>
+        <v>122478633</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>105308</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1026,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591053</v>
+        <v>591057</v>
       </c>
       <c r="R5" t="n">
-        <v>6440547</v>
+        <v>6440531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478614</v>
+        <v>122478814</v>
       </c>
       <c r="B6" t="n">
-        <v>57749</v>
+        <v>98202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,39 +1137,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591079</v>
+        <v>591015</v>
       </c>
       <c r="R6" t="n">
-        <v>6440534</v>
+        <v>6440575</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,7 +1236,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478809</v>
+        <v>122478625</v>
       </c>
       <c r="B7" t="n">
         <v>98202</v>
@@ -1280,14 +1280,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591050</v>
+        <v>591062</v>
       </c>
       <c r="R7" t="n">
-        <v>6440530</v>
+        <v>6440546</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478625</v>
+        <v>122478630</v>
       </c>
       <c r="B8" t="n">
         <v>98202</v>
@@ -1391,14 +1391,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591062</v>
+        <v>591053</v>
       </c>
       <c r="R8" t="n">
-        <v>6440546</v>
+        <v>6440547</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478614</v>
+        <v>122478625</v>
       </c>
       <c r="B2" t="n">
-        <v>57749</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591079</v>
+        <v>591062</v>
       </c>
       <c r="R2" t="n">
-        <v>6440534</v>
+        <v>6440546</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478832</v>
+        <v>122478809</v>
       </c>
       <c r="B3" t="n">
-        <v>57749</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,39 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +824,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591009</v>
+        <v>591050</v>
       </c>
       <c r="R3" t="n">
-        <v>6440585</v>
+        <v>6440530</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478809</v>
+        <v>122478814</v>
       </c>
       <c r="B4" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,11 +904,6 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -951,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591050</v>
+        <v>591015</v>
       </c>
       <c r="R4" t="n">
-        <v>6440530</v>
+        <v>6440575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478633</v>
+        <v>122478832</v>
       </c>
       <c r="B5" t="n">
-        <v>105308</v>
+        <v>57749</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,31 +1009,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,13 +1040,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591057</v>
+        <v>591009</v>
       </c>
       <c r="R5" t="n">
-        <v>6440531</v>
+        <v>6440585</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1106,7 +1084,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478814</v>
+        <v>122478614</v>
       </c>
       <c r="B6" t="n">
-        <v>98202</v>
+        <v>57749</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,35 +1114,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,13 +1149,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591015</v>
+        <v>591079</v>
       </c>
       <c r="R6" t="n">
-        <v>6440575</v>
+        <v>6440534</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1193,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478625</v>
+        <v>122478633</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>105317</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,25 +1223,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,14 +1250,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591062</v>
+        <v>591057</v>
       </c>
       <c r="R7" t="n">
-        <v>6440546</v>
+        <v>6440531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1320,7 @@
         <v>122478630</v>
       </c>
       <c r="B8" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,11 +1334,6 @@
       </c>
       <c r="E8" t="n">
         <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122478625</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478809</v>
+        <v>122478633</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>105330</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,20 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591050</v>
+        <v>591057</v>
       </c>
       <c r="R3" t="n">
-        <v>6440530</v>
+        <v>6440531</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478814</v>
+        <v>122478832</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>57753</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +909,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591015</v>
+        <v>591009</v>
       </c>
       <c r="R4" t="n">
-        <v>6440575</v>
+        <v>6440585</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +993,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478832</v>
+        <v>122478614</v>
       </c>
       <c r="B5" t="n">
-        <v>57749</v>
+        <v>57753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,6 +1028,11 @@
       </c>
       <c r="E5" t="n">
         <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1040,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591009</v>
+        <v>591079</v>
       </c>
       <c r="R5" t="n">
-        <v>6440585</v>
+        <v>6440534</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1102,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478614</v>
+        <v>122478814</v>
       </c>
       <c r="B6" t="n">
-        <v>57749</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,34 +1137,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591079</v>
+        <v>591015</v>
       </c>
       <c r="R6" t="n">
-        <v>6440534</v>
+        <v>6440575</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478633</v>
+        <v>122478630</v>
       </c>
       <c r="B7" t="n">
-        <v>105317</v>
+        <v>98224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,20 +1248,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1254,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591057</v>
+        <v>591053</v>
       </c>
       <c r="R7" t="n">
-        <v>6440531</v>
+        <v>6440547</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478630</v>
+        <v>122478809</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1334,6 +1364,11 @@
       </c>
       <c r="E8" t="n">
         <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1360,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591053</v>
+        <v>591050</v>
       </c>
       <c r="R8" t="n">
-        <v>6440547</v>
+        <v>6440530</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478625</v>
+        <v>122478630</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -719,14 +719,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591062</v>
+        <v>591053</v>
       </c>
       <c r="R2" t="n">
-        <v>6440546</v>
+        <v>6440547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478633</v>
+        <v>122478832</v>
       </c>
       <c r="B3" t="n">
-        <v>105330</v>
+        <v>57753</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,31 +802,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591057</v>
+        <v>591009</v>
       </c>
       <c r="R3" t="n">
-        <v>6440531</v>
+        <v>6440585</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478832</v>
+        <v>122478809</v>
       </c>
       <c r="B4" t="n">
-        <v>57753</v>
+        <v>98237</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,39 +912,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591009</v>
+        <v>591050</v>
       </c>
       <c r="R4" t="n">
-        <v>6440585</v>
+        <v>6440530</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,6 +992,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478614</v>
+        <v>122478633</v>
       </c>
       <c r="B5" t="n">
-        <v>57753</v>
+        <v>105343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,35 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1063,13 +1059,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591079</v>
+        <v>591057</v>
       </c>
       <c r="R5" t="n">
-        <v>6440534</v>
+        <v>6440531</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,6 +1103,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1128,7 +1125,7 @@
         <v>122478814</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1236,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478630</v>
+        <v>122478614</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>57753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,35 +1245,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591053</v>
+        <v>591079</v>
       </c>
       <c r="R7" t="n">
-        <v>6440547</v>
+        <v>6440534</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478809</v>
+        <v>122478625</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,14 +1391,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591050</v>
+        <v>591062</v>
       </c>
       <c r="R8" t="n">
-        <v>6440530</v>
+        <v>6440546</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478630</v>
+        <v>122478814</v>
       </c>
       <c r="B2" t="n">
         <v>98237</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591053</v>
+        <v>591015</v>
       </c>
       <c r="R2" t="n">
-        <v>6440547</v>
+        <v>6440575</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478832</v>
+        <v>122478630</v>
       </c>
       <c r="B3" t="n">
-        <v>57753</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591009</v>
+        <v>591053</v>
       </c>
       <c r="R3" t="n">
-        <v>6440585</v>
+        <v>6440547</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478809</v>
+        <v>122478633</v>
       </c>
       <c r="B4" t="n">
-        <v>98237</v>
+        <v>105343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591050</v>
+        <v>591057</v>
       </c>
       <c r="R4" t="n">
-        <v>6440530</v>
+        <v>6440531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478633</v>
+        <v>122478614</v>
       </c>
       <c r="B5" t="n">
-        <v>105343</v>
+        <v>57753</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,31 +1024,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591057</v>
+        <v>591079</v>
       </c>
       <c r="R5" t="n">
-        <v>6440531</v>
+        <v>6440534</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478814</v>
+        <v>122478809</v>
       </c>
       <c r="B6" t="n">
         <v>98237</v>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591015</v>
+        <v>591050</v>
       </c>
       <c r="R6" t="n">
-        <v>6440575</v>
+        <v>6440530</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478614</v>
+        <v>122478625</v>
       </c>
       <c r="B7" t="n">
-        <v>57753</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,53 +1245,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591079</v>
+        <v>591062</v>
       </c>
       <c r="R7" t="n">
-        <v>6440534</v>
+        <v>6440546</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,6 +1325,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478625</v>
+        <v>122478832</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>57753</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,49 +1356,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591062</v>
+        <v>591009</v>
       </c>
       <c r="R8" t="n">
-        <v>6440546</v>
+        <v>6440585</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478814</v>
+        <v>122478614</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>57753</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591015</v>
+        <v>591079</v>
       </c>
       <c r="R2" t="n">
-        <v>6440575</v>
+        <v>6440534</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +792,7 @@
         <v>122478630</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478633</v>
+        <v>122478814</v>
       </c>
       <c r="B4" t="n">
-        <v>105343</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591057</v>
+        <v>591015</v>
       </c>
       <c r="R4" t="n">
-        <v>6440531</v>
+        <v>6440575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478614</v>
+        <v>122478633</v>
       </c>
       <c r="B5" t="n">
-        <v>57753</v>
+        <v>105346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,35 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,13 +1059,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591079</v>
+        <v>591057</v>
       </c>
       <c r="R5" t="n">
-        <v>6440534</v>
+        <v>6440531</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,6 +1103,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478809</v>
+        <v>122478832</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>57753</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591050</v>
+        <v>591009</v>
       </c>
       <c r="R6" t="n">
-        <v>6440530</v>
+        <v>6440585</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,7 +1239,7 @@
         <v>122478625</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478832</v>
+        <v>122478809</v>
       </c>
       <c r="B8" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,39 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591009</v>
+        <v>591050</v>
       </c>
       <c r="R8" t="n">
-        <v>6440585</v>
+        <v>6440530</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1439,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478614</v>
+        <v>122478633</v>
       </c>
       <c r="B2" t="n">
-        <v>57753</v>
+        <v>105346</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591079</v>
+        <v>591057</v>
       </c>
       <c r="R2" t="n">
-        <v>6440534</v>
+        <v>6440531</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478630</v>
+        <v>122478814</v>
       </c>
       <c r="B3" t="n">
         <v>98240</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591053</v>
+        <v>591015</v>
       </c>
       <c r="R3" t="n">
-        <v>6440547</v>
+        <v>6440575</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478814</v>
+        <v>122478809</v>
       </c>
       <c r="B4" t="n">
         <v>98240</v>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591015</v>
+        <v>591050</v>
       </c>
       <c r="R4" t="n">
-        <v>6440575</v>
+        <v>6440530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478633</v>
+        <v>122478630</v>
       </c>
       <c r="B5" t="n">
-        <v>105346</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591057</v>
+        <v>591053</v>
       </c>
       <c r="R5" t="n">
-        <v>6440531</v>
+        <v>6440547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478832</v>
+        <v>122478625</v>
       </c>
       <c r="B6" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,53 +1131,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591009</v>
+        <v>591062</v>
       </c>
       <c r="R6" t="n">
-        <v>6440585</v>
+        <v>6440546</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1211,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478625</v>
+        <v>122478614</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>57753</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,49 +1242,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591062</v>
+        <v>591079</v>
       </c>
       <c r="R7" t="n">
-        <v>6440546</v>
+        <v>6440534</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1326,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478809</v>
+        <v>122478832</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>57753</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,35 +1356,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591050</v>
+        <v>591009</v>
       </c>
       <c r="R8" t="n">
-        <v>6440530</v>
+        <v>6440585</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478633</v>
+        <v>122478630</v>
       </c>
       <c r="B2" t="n">
-        <v>105346</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591057</v>
+        <v>591053</v>
       </c>
       <c r="R2" t="n">
-        <v>6440531</v>
+        <v>6440547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478814</v>
+        <v>122478614</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>57754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591015</v>
+        <v>591079</v>
       </c>
       <c r="R3" t="n">
-        <v>6440575</v>
+        <v>6440534</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478809</v>
+        <v>122478814</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591050</v>
+        <v>591015</v>
       </c>
       <c r="R4" t="n">
-        <v>6440530</v>
+        <v>6440575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478630</v>
+        <v>122478832</v>
       </c>
       <c r="B5" t="n">
-        <v>98240</v>
+        <v>57754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,35 +1023,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591053</v>
+        <v>591009</v>
       </c>
       <c r="R5" t="n">
-        <v>6440547</v>
+        <v>6440585</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1119,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478625</v>
+        <v>122478809</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,14 +1169,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591062</v>
+        <v>591050</v>
       </c>
       <c r="R6" t="n">
-        <v>6440546</v>
+        <v>6440530</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478614</v>
+        <v>122478625</v>
       </c>
       <c r="B7" t="n">
-        <v>57753</v>
+        <v>98241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,53 +1248,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591079</v>
+        <v>591062</v>
       </c>
       <c r="R7" t="n">
-        <v>6440534</v>
+        <v>6440546</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,6 +1328,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478832</v>
+        <v>122478633</v>
       </c>
       <c r="B8" t="n">
-        <v>57753</v>
+        <v>105347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,35 +1363,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591009</v>
+        <v>591057</v>
       </c>
       <c r="R8" t="n">
-        <v>6440585</v>
+        <v>6440531</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1439,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478630</v>
+        <v>122478614</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>57754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591053</v>
+        <v>591079</v>
       </c>
       <c r="R2" t="n">
-        <v>6440547</v>
+        <v>6440534</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478614</v>
+        <v>122478809</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591079</v>
+        <v>591050</v>
       </c>
       <c r="R3" t="n">
-        <v>6440534</v>
+        <v>6440530</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478814</v>
+        <v>122478633</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>105350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591015</v>
+        <v>591057</v>
       </c>
       <c r="R4" t="n">
-        <v>6440575</v>
+        <v>6440531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478832</v>
+        <v>122478625</v>
       </c>
       <c r="B5" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,53 +1023,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591009</v>
+        <v>591062</v>
       </c>
       <c r="R5" t="n">
-        <v>6440585</v>
+        <v>6440546</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,6 +1103,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478809</v>
+        <v>122478832</v>
       </c>
       <c r="B6" t="n">
-        <v>98241</v>
+        <v>57754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,35 +1134,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591050</v>
+        <v>591009</v>
       </c>
       <c r="R6" t="n">
-        <v>6440530</v>
+        <v>6440585</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478625</v>
+        <v>122478630</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,14 +1280,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591062</v>
+        <v>591053</v>
       </c>
       <c r="R7" t="n">
-        <v>6440546</v>
+        <v>6440547</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478633</v>
+        <v>122478814</v>
       </c>
       <c r="B8" t="n">
-        <v>105347</v>
+        <v>98244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591057</v>
+        <v>591015</v>
       </c>
       <c r="R8" t="n">
-        <v>6440531</v>
+        <v>6440575</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478614</v>
+        <v>122478809</v>
       </c>
       <c r="B2" t="n">
-        <v>57754</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591079</v>
+        <v>591050</v>
       </c>
       <c r="R2" t="n">
-        <v>6440534</v>
+        <v>6440530</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478809</v>
+        <v>122478625</v>
       </c>
       <c r="B3" t="n">
         <v>98244</v>
@@ -833,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591050</v>
+        <v>591062</v>
       </c>
       <c r="R3" t="n">
-        <v>6440530</v>
+        <v>6440546</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478633</v>
+        <v>122478630</v>
       </c>
       <c r="B4" t="n">
-        <v>105350</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591057</v>
+        <v>591053</v>
       </c>
       <c r="R4" t="n">
-        <v>6440531</v>
+        <v>6440547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478625</v>
+        <v>122478633</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>105350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,14 +1052,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591062</v>
+        <v>591057</v>
       </c>
       <c r="R5" t="n">
-        <v>6440546</v>
+        <v>6440531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1236,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478630</v>
+        <v>122478814</v>
       </c>
       <c r="B7" t="n">
         <v>98244</v>
@@ -1284,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591053</v>
+        <v>591015</v>
       </c>
       <c r="R7" t="n">
-        <v>6440547</v>
+        <v>6440575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478814</v>
+        <v>122478614</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
+        <v>57754</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,35 +1356,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591015</v>
+        <v>591079</v>
       </c>
       <c r="R8" t="n">
-        <v>6440575</v>
+        <v>6440534</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478809</v>
+        <v>122478832</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591050</v>
+        <v>591009</v>
       </c>
       <c r="R2" t="n">
-        <v>6440530</v>
+        <v>6440585</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,7 +792,7 @@
         <v>122478625</v>
       </c>
       <c r="B3" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +903,7 @@
         <v>122478630</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478633</v>
+        <v>122478809</v>
       </c>
       <c r="B5" t="n">
-        <v>105350</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591057</v>
+        <v>591050</v>
       </c>
       <c r="R5" t="n">
-        <v>6440531</v>
+        <v>6440530</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478832</v>
+        <v>122478814</v>
       </c>
       <c r="B6" t="n">
-        <v>57754</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591009</v>
+        <v>591015</v>
       </c>
       <c r="R6" t="n">
-        <v>6440585</v>
+        <v>6440575</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478814</v>
+        <v>122478633</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>105453</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591015</v>
+        <v>591057</v>
       </c>
       <c r="R7" t="n">
-        <v>6440575</v>
+        <v>6440531</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
         <v>122478614</v>
       </c>
       <c r="B8" t="n">
-        <v>57754</v>
+        <v>57848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478633</v>
+        <v>122478614</v>
       </c>
       <c r="B7" t="n">
-        <v>105453</v>
+        <v>57848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,31 +1249,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591057</v>
+        <v>591079</v>
       </c>
       <c r="R7" t="n">
-        <v>6440531</v>
+        <v>6440534</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,7 +1329,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478614</v>
+        <v>122478633</v>
       </c>
       <c r="B8" t="n">
-        <v>57848</v>
+        <v>105453</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,35 +1363,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1396,13 +1395,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591079</v>
+        <v>591057</v>
       </c>
       <c r="R8" t="n">
-        <v>6440534</v>
+        <v>6440531</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1439,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478625</v>
+        <v>122478814</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,14 +833,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591062</v>
+        <v>591015</v>
       </c>
       <c r="R3" t="n">
-        <v>6440546</v>
+        <v>6440575</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -903,7 +903,7 @@
         <v>122478630</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478809</v>
+        <v>122478625</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,14 +1055,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591050</v>
+        <v>591062</v>
       </c>
       <c r="R5" t="n">
-        <v>6440530</v>
+        <v>6440546</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478814</v>
+        <v>122478614</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591015</v>
+        <v>591079</v>
       </c>
       <c r="R6" t="n">
-        <v>6440575</v>
+        <v>6440534</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478614</v>
+        <v>122478809</v>
       </c>
       <c r="B7" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,39 +1248,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,13 +1284,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591079</v>
+        <v>591050</v>
       </c>
       <c r="R7" t="n">
-        <v>6440534</v>
+        <v>6440530</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,6 +1328,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>122478633</v>
       </c>
       <c r="B8" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478832</v>
+        <v>122478630</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591009</v>
+        <v>591053</v>
       </c>
       <c r="R2" t="n">
-        <v>6440585</v>
+        <v>6440547</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478814</v>
+        <v>122478832</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591015</v>
+        <v>591009</v>
       </c>
       <c r="R3" t="n">
-        <v>6440575</v>
+        <v>6440585</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478630</v>
+        <v>122478809</v>
       </c>
       <c r="B4" t="n">
         <v>98355</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591053</v>
+        <v>591050</v>
       </c>
       <c r="R4" t="n">
-        <v>6440547</v>
+        <v>6440530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478625</v>
+        <v>122478633</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1055,14 +1055,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591062</v>
+        <v>591057</v>
       </c>
       <c r="R5" t="n">
-        <v>6440546</v>
+        <v>6440531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478614</v>
+        <v>122478814</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,39 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591079</v>
+        <v>591015</v>
       </c>
       <c r="R6" t="n">
-        <v>6440534</v>
+        <v>6440575</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,7 +1233,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478809</v>
+        <v>122478625</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1280,14 +1277,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591050</v>
+        <v>591062</v>
       </c>
       <c r="R7" t="n">
-        <v>6440530</v>
+        <v>6440546</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478633</v>
+        <v>122478614</v>
       </c>
       <c r="B8" t="n">
-        <v>105461</v>
+        <v>57848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,31 +1360,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,13 +1396,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591057</v>
+        <v>591079</v>
       </c>
       <c r="R8" t="n">
-        <v>6440531</v>
+        <v>6440534</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,7 +1440,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4454-2025 artfynd.xlsx
+++ b/artfynd/A 4454-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478630</v>
+        <v>122478809</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591053</v>
+        <v>591050</v>
       </c>
       <c r="R2" t="n">
-        <v>6440547</v>
+        <v>6440530</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478832</v>
+        <v>122478630</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,39 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591009</v>
+        <v>591053</v>
       </c>
       <c r="R3" t="n">
-        <v>6440585</v>
+        <v>6440547</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +878,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478809</v>
+        <v>122478633</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591050</v>
+        <v>591057</v>
       </c>
       <c r="R4" t="n">
-        <v>6440530</v>
+        <v>6440531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478633</v>
+        <v>122478832</v>
       </c>
       <c r="B5" t="n">
-        <v>105461</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,31 +1024,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591057</v>
+        <v>591009</v>
       </c>
       <c r="R5" t="n">
-        <v>6440531</v>
+        <v>6440585</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478814</v>
+        <v>122478614</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591015</v>
+        <v>591079</v>
       </c>
       <c r="R6" t="n">
-        <v>6440575</v>
+        <v>6440534</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478625</v>
+        <v>122478814</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,14 +1280,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>A  4454, Rammsjön, Sm</t>
+          <t>A 4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591062</v>
+        <v>591015</v>
       </c>
       <c r="R7" t="n">
-        <v>6440546</v>
+        <v>6440575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478614</v>
+        <v>122478625</v>
       </c>
       <c r="B8" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,53 +1359,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 4454, Rammsjön, Sm</t>
+          <t>A  4454, Rammsjön, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591079</v>
+        <v>591062</v>
       </c>
       <c r="R8" t="n">
-        <v>6440534</v>
+        <v>6440546</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,6 +1439,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
